--- a/private/intl/do/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/do/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Prestaciones laborales»: pones tus fechas, tu salario promedio y cómo terminó el contrato, y te dice el preaviso, la cesantía, las vacaciones y la regalía.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 8/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 9/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -284,7 +284,7 @@
     <t>Tablas oficiales de República Dominicana</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 8/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 9/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -1590,7 +1590,7 @@
         <v>54</v>
       </c>
       <c r="B6" s="17">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>55</v>

--- a/private/intl/do/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/do/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Prestaciones laborales»: pones tus fechas, tu salario promedio y cómo terminó el contrato, y te dice el preaviso, la cesantía, las vacaciones y la regalía.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 9/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 13/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -284,7 +284,7 @@
     <t>Tablas oficiales de República Dominicana</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 9/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 13/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -1590,7 +1590,7 @@
         <v>54</v>
       </c>
       <c r="B6" s="17">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>55</v>

--- a/private/intl/do/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/do/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Prestaciones laborales»: pones tus fechas, tu salario promedio y cómo terminó el contrato, y te dice el preaviso, la cesantía, las vacaciones y la regalía.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 9/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 14/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -284,7 +284,7 @@
     <t>Tablas oficiales de República Dominicana</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 9/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 14/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -1590,7 +1590,7 @@
         <v>54</v>
       </c>
       <c r="B6" s="17">
-        <v>46304</v>
+        <v>46309</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>55</v>

--- a/private/intl/do/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/do/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Prestaciones laborales»: pones tus fechas, tu salario promedio y cómo terminó el contrato, y te dice el preaviso, la cesantía, las vacaciones y la regalía.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 14/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 15/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -284,7 +284,7 @@
     <t>Tablas oficiales de República Dominicana</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 14/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 15/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -1590,7 +1590,7 @@
         <v>54</v>
       </c>
       <c r="B6" s="17">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>55</v>

--- a/private/intl/do/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/do/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Prestaciones laborales»: pones tus fechas, tu salario promedio y cómo terminó el contrato, y te dice el preaviso, la cesantía, las vacaciones y la regalía.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 15/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 16/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -284,7 +284,7 @@
     <t>Tablas oficiales de República Dominicana</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 15/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 16/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -1590,7 +1590,7 @@
         <v>54</v>
       </c>
       <c r="B6" s="17">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>55</v>

--- a/private/intl/do/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/do/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Prestaciones laborales»: pones tus fechas, tu salario promedio y cómo terminó el contrato, y te dice el preaviso, la cesantía, las vacaciones y la regalía.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 16/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 19/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -284,7 +284,7 @@
     <t>Tablas oficiales de República Dominicana</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 16/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 19/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -1590,7 +1590,7 @@
         <v>54</v>
       </c>
       <c r="B6" s="17">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>55</v>

--- a/private/intl/do/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/do/sueldo-y-liquidacion-2026.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="142">
   <si>
     <t>Planilla de salario y prestaciones República Dominicana 2026</t>
   </si>
@@ -32,7 +32,7 @@
     <t>«Prestaciones laborales»: pones tus fechas, tu salario promedio y cómo terminó el contrato, y te dice el preaviso, la cesantía, las vacaciones y la regalía.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 19/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 20/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -98,9 +98,21 @@
     <t>Regalía pascual (salario de Navidad)</t>
   </si>
   <si>
+    <t>Empresa grande</t>
+  </si>
+  <si>
+    <t>Empresa mediana</t>
+  </si>
+  <si>
+    <t>Empresa pequeña</t>
+  </si>
+  <si>
     <t>Año: desde</t>
   </si>
   <si>
+    <t>Microempresa</t>
+  </si>
+  <si>
     <t>Salario mensual</t>
   </si>
   <si>
@@ -131,9 +143,6 @@
     <t>Tamaño de la empresa</t>
   </si>
   <si>
-    <t>Empresa grande</t>
-  </si>
-  <si>
     <t>Salario ganado en el año</t>
   </si>
   <si>
@@ -284,7 +293,7 @@
     <t>Tablas oficiales de República Dominicana</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 19/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 20/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -363,15 +372,6 @@
   </si>
   <si>
     <t>https://mt.gob.do/ministerio-de-trabajo-llama-a-empresarios-a-cumplir-con-el-pago-del-aumento-del-8-del-salario-minimo/</t>
-  </si>
-  <si>
-    <t>Empresa mediana</t>
-  </si>
-  <si>
-    <t>Empresa pequeña</t>
-  </si>
-  <si>
-    <t>Microempresa</t>
   </si>
   <si>
     <t>Tope del salario de Navidad en salarios mínimos</t>
@@ -1319,7 +1319,7 @@
   <sheetPr>
     <tabColor rgb="FF1B5E20"/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:Z19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -1328,46 +1328,61 @@
     <col min="4" max="4" width="3" customWidth="1"/>
     <col min="5" max="5" width="50" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="26" max="26" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>26</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
-    </row>
-    <row r="3" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="Z1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="26:26" x14ac:dyDescent="0.25">
+      <c r="Z2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="5:26" x14ac:dyDescent="0.25">
       <c r="E3" s="6" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="6"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="Z3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
       <c r="E4" s="7" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F4" s="16">
         <f>IF(AND(ISNUMBER(B6),B6&gt;DATE(YEAR(B9),1,1)),B6,DATE(YEAR(B9),1,1))</f>
       </c>
+      <c r="Z4" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B5" s="10">
         <v>40000</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F5" s="16">
         <f>IF(AND(ISNUMBER(B7),B7&lt;DATE(YEAR(B9),12,31)),B7,DATE(YEAR(B9),12,31))</f>
@@ -1375,14 +1390,14 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B6" s="17"/>
       <c r="C6" s="11" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F6" s="18">
         <f>MIN(12,IF(EDATE(F4,((YEAR((F5+1))-YEAR(F4))*12+MONTH((F5+1))-MONTH(F4)))&gt;(F5+1),((YEAR((F5+1))-YEAR(F4))*12+MONTH((F5+1))-MONTH(F4))-1,((YEAR((F5+1))-YEAR(F4))*12+MONTH((F5+1))-MONTH(F4))))</f>
@@ -1390,14 +1405,14 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B7" s="17"/>
       <c r="C7" s="11" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F7" s="19">
         <f>IF(F5&lt;F4,0,MIN(12,F6+((F5+1)-EDATE(F4,F6))/30))</f>
@@ -1405,13 +1420,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F8" s="8">
         <f>ROUND(B5*F7,2)</f>
@@ -1419,16 +1434,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B9" s="17">
         <f>TODAY()</f>
       </c>
       <c r="C9" s="11" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F9" s="8">
         <f>ROUND(F8/12,2)</f>
@@ -1436,7 +1451,7 @@
     </row>
     <row r="10" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E10" s="7" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F10" s="8">
         <f>ROUND(INDEX('Tablas oficiales'!$C$15:$C$18,MATCH(B8,'Tablas oficiales'!$B$15:$B$18,0))*'Tablas oficiales'!$C$19,2)</f>
@@ -1444,7 +1459,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -1458,7 +1473,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B13" s="22">
         <f>ROUND(F7,2)</f>
@@ -1466,7 +1481,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B14" s="13">
         <f>F8</f>
@@ -1474,7 +1489,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B15" s="13">
         <f>F9</f>
@@ -1482,7 +1497,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B16" s="13">
         <f>F10</f>
@@ -1490,7 +1505,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B17" s="15">
         <f>MIN(F9,F10)</f>
@@ -1498,7 +1513,7 @@
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -1520,8 +1535,8 @@
     <dataValidation type="date" operator="greaterThan" allowBlank="1" showErrorMessage="1" error="Escribe una fecha como dd/mm/aaaa." sqref="B6:B7">
       <formula1>18264</formula1>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista." sqref="B8">
-      <formula1>'Tablas oficiales'!$B$15:$B$18</formula1>
+    <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista (Tamaño de la empresa)." sqref="B8">
+      <formula1>'Regalía pascual'!$Z$1:$Z$4</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1534,7 +1549,7 @@
   <sheetPr>
     <tabColor rgb="FF1B5E20"/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:Z26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -1543,43 +1558,58 @@
     <col min="4" max="4" width="3" customWidth="1"/>
     <col min="5" max="5" width="50" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="26" max="26" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
-    </row>
-    <row r="3" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="Z1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="26:26" x14ac:dyDescent="0.25">
+      <c r="Z2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="5:26" x14ac:dyDescent="0.25">
       <c r="E3" s="6" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="6"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="Z3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
       <c r="E4" s="7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F4" s="18">
         <f>IF(EDATE(B5,12*(YEAR(B6)-YEAR(B5)))&gt;B6,(YEAR(B6)-YEAR(B5))-1,(YEAR(B6)-YEAR(B5)))</f>
       </c>
+      <c r="Z4" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B5" s="17">
         <v>44635</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F5" s="16">
         <f>EDATE(B5,12*F4)</f>
@@ -1587,13 +1617,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B6" s="17">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F6" s="18">
         <f>MIN(12,IF(EDATE(F5,((YEAR(B6)-YEAR(F5))*12+MONTH(B6)-MONTH(F5)))&gt;B6,((YEAR(B6)-YEAR(F5))*12+MONTH(B6)-MONTH(F5))-1,((YEAR(B6)-YEAR(F5))*12+MONTH(B6)-MONTH(F5))))</f>
@@ -1601,16 +1631,16 @@
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B7" s="10">
         <v>40000</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F7" s="18">
         <f>B6-EDATE(F5,F6)</f>
@@ -1618,13 +1648,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F8" s="8">
         <f>ROUND(B7/'Tablas oficiales'!$C$20,2)</f>
@@ -1632,35 +1662,35 @@
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B10" s="23">
         <v>0</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F11" s="19">
         <f>IF(AND(OR(B8="Me desahuciaron (despido sin alegar causa)",B8="Despido injustificado o dimisión justificada"),OR(B8="Despido injustificado o dimisión justificada",AND(B8="Me desahuciaron (despido sin alegar causa)",B9="No"))),IF(F4&gt;=1,'Tablas oficiales'!$C$23,IF(F6&lt;3,0,IF(OR(F6&lt;6,AND(F6=6,F7=0)),'Tablas oficiales'!$C$21,'Tablas oficiales'!$C$22))),0)</f>
@@ -1668,7 +1698,7 @@
     </row>
     <row r="12" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E12" s="7" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F12" s="19">
         <f>IF(OR(B8="Me desahuciaron (despido sin alegar causa)",B8="Despido injustificado o dimisión justificada"),IF(F4=0,IF(OR(F6&lt;3),0,IF(OR(F6&lt;6,AND(F6=6,F7=0)),'Tablas oficiales'!$C$24,'Tablas oficiales'!$C$25)),F4*IF(F4&gt;=5,'Tablas oficiales'!$C$27,'Tablas oficiales'!$C$26)+IF(OR(F6&lt;3,AND(F6=3,F7=0)),0,IF(OR(F6&lt;6,AND(F6=6,F7=0)),'Tablas oficiales'!$C$24,'Tablas oficiales'!$C$25))),0)</f>
@@ -1676,7 +1706,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -1688,18 +1718,18 @@
       <c r="B14" s="21"/>
       <c r="C14" s="21"/>
       <c r="E14" s="24" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B15" s="25">
         <f>F4&amp;" años, "&amp;F6&amp;" meses y "&amp;F7&amp;" días"</f>
       </c>
       <c r="E15" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F15" s="18">
         <f>IF(F7&gt;0,F6,F6-1)</f>
@@ -1707,13 +1737,13 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B16" s="13">
         <f>F8</f>
       </c>
       <c r="E16" s="7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F16" s="19">
         <f>IF(F15&lt;5,0,CHOOSE(MIN(F15,11)-4,'Tablas oficiales'!$C$28,'Tablas oficiales'!$C$29,'Tablas oficiales'!$C$30,'Tablas oficiales'!$C$31,'Tablas oficiales'!$C$32,'Tablas oficiales'!$C$33,'Tablas oficiales'!$C$34))+B10</f>
@@ -1721,13 +1751,13 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B17" s="22">
         <f>F11</f>
       </c>
       <c r="E17" s="7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F17" s="16">
         <f>IF(AND(ISNUMBER(B5),B5&gt;DATE(YEAR(B6),1,1)),B5,DATE(YEAR(B6),1,1))</f>
@@ -1735,13 +1765,13 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B18" s="13">
         <f>F23</f>
       </c>
       <c r="E18" s="7" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F18" s="16">
         <f>IF(AND(ISNUMBER(B6),B6&lt;DATE(YEAR(B6),12,31)),B6,DATE(YEAR(B6),12,31))</f>
@@ -1749,13 +1779,13 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B19" s="22">
         <f>F12</f>
       </c>
       <c r="E19" s="7" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F19" s="18">
         <f>MIN(12,IF(EDATE(F17,((YEAR((F18+1))-YEAR(F17))*12+MONTH((F18+1))-MONTH(F17)))&gt;(F18+1),((YEAR((F18+1))-YEAR(F17))*12+MONTH((F18+1))-MONTH(F17))-1,((YEAR((F18+1))-YEAR(F17))*12+MONTH((F18+1))-MONTH(F17))))</f>
@@ -1763,13 +1793,13 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B20" s="13">
         <f>F24</f>
       </c>
       <c r="E20" s="7" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F20" s="19">
         <f>IF(F18&lt;F17,0,MIN(12,F19+((F18+1)-EDATE(F17,F19))/30))</f>
@@ -1777,13 +1807,13 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B21" s="22">
         <f>F16</f>
       </c>
       <c r="E21" s="7" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F21" s="8">
         <f>ROUND(INDEX('Tablas oficiales'!$C$15:$C$18,MATCH(B11,'Tablas oficiales'!$B$15:$B$18,0))*'Tablas oficiales'!$C$19,2)</f>
@@ -1791,13 +1821,13 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B22" s="13">
         <f>F25</f>
       </c>
       <c r="E22" s="7" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F22" s="8">
         <f>MIN(ROUND(B7*F20/12,2),F21)</f>
@@ -1805,13 +1835,13 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B23" s="13">
         <f>F22</f>
       </c>
       <c r="E23" s="7" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F23" s="8">
         <f>ROUND(F8*F11,2)</f>
@@ -1819,13 +1849,13 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B24" s="15">
         <f>ROUND(F23+F24+F25+F22,2)</f>
       </c>
       <c r="E24" s="7" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F24" s="8">
         <f>ROUND(F8*F12,2)</f>
@@ -1833,7 +1863,7 @@
     </row>
     <row r="25" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E25" s="7" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F25" s="8">
         <f>ROUND(F8*F16,2)</f>
@@ -1841,7 +1871,7 @@
     </row>
     <row r="26" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -1860,8 +1890,8 @@
       <formula1>0</formula1>
       <formula2>1000000000000</formula2>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista." sqref="B11">
-      <formula1>'Tablas oficiales'!$B$15:$B$18</formula1>
+    <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista (Tamaño de la empresa)." sqref="B11">
+      <formula1>'Prestaciones laborales'!$Z$1:$Z$4</formula1>
     </dataValidation>
     <dataValidation type="date" operator="greaterThan" allowBlank="1" showErrorMessage="1" error="Escribe una fecha como dd/mm/aaaa." sqref="B5:B6">
       <formula1>18264</formula1>
@@ -1901,7 +1931,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B1" s="26"/>
       <c r="C1" s="26"/>
@@ -1912,7 +1942,7 @@
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -1923,150 +1953,150 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B3" s="27" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D3" s="27" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E3" s="27" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F3" s="27" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G3" s="27" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="28" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B4" s="28" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C4" s="29">
         <v>232230</v>
       </c>
       <c r="D4" s="28" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E4" s="28" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F4" s="30" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G4" s="28" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="31" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C5" s="32">
         <v>3.04</v>
       </c>
       <c r="D5" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="E5" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="F5" s="33" t="s">
         <v>104</v>
       </c>
-      <c r="E5" s="31" t="s">
-        <v>100</v>
-      </c>
-      <c r="F5" s="33" t="s">
-        <v>101</v>
-      </c>
       <c r="G5" s="31" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="28" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C6" s="29">
         <v>464460</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F6" s="30" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="31" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C7" s="32">
         <v>2.87</v>
       </c>
       <c r="D7" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="E7" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="F7" s="33" t="s">
         <v>104</v>
       </c>
-      <c r="E7" s="31" t="s">
-        <v>100</v>
-      </c>
-      <c r="F7" s="33" t="s">
-        <v>101</v>
-      </c>
       <c r="G7" s="31" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="34" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B8" s="35"/>
       <c r="C8" s="35"/>
       <c r="D8" s="35" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E8" s="35" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F8" s="36" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="G8" s="35" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" s="37" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C9" s="37" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D9" s="37" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E9" s="37" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.25">
@@ -2127,94 +2157,94 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="28" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B15" s="28" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="C15" s="29">
         <v>29988</v>
       </c>
       <c r="D15" s="28" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E15" s="28" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F15" s="30" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G15" s="28" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="31" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>116</v>
+        <v>28</v>
       </c>
       <c r="C16" s="41">
         <v>27489.6</v>
       </c>
       <c r="D16" s="31" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E16" s="31" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F16" s="33" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G16" s="31" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="28" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B17" s="28" t="s">
-        <v>117</v>
+        <v>29</v>
       </c>
       <c r="C17" s="29">
         <v>18421.2</v>
       </c>
       <c r="D17" s="28" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E17" s="28" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F17" s="30" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G17" s="28" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="31" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B18" s="31" t="s">
-        <v>118</v>
+        <v>31</v>
       </c>
       <c r="C18" s="41">
         <v>16993.2</v>
       </c>
       <c r="D18" s="31" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E18" s="31" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F18" s="33" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G18" s="31" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -2222,13 +2252,13 @@
         <v>119</v>
       </c>
       <c r="B19" s="28" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C19" s="42">
         <v>5</v>
       </c>
       <c r="D19" s="28" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E19" s="28" t="s">
         <v>120</v>
@@ -2237,7 +2267,7 @@
         <v>121</v>
       </c>
       <c r="G19" s="28" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -2245,7 +2275,7 @@
         <v>122</v>
       </c>
       <c r="B20" s="31" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C20" s="32">
         <v>23.83</v>
@@ -2260,7 +2290,7 @@
         <v>121</v>
       </c>
       <c r="G20" s="31" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -2283,7 +2313,7 @@
         <v>121</v>
       </c>
       <c r="G21" s="28" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -2306,7 +2336,7 @@
         <v>121</v>
       </c>
       <c r="G22" s="31" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -2329,7 +2359,7 @@
         <v>121</v>
       </c>
       <c r="G23" s="28" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -2352,7 +2382,7 @@
         <v>121</v>
       </c>
       <c r="G24" s="31" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -2375,7 +2405,7 @@
         <v>121</v>
       </c>
       <c r="G25" s="28" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -2398,7 +2428,7 @@
         <v>121</v>
       </c>
       <c r="G26" s="31" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -2421,7 +2451,7 @@
         <v>121</v>
       </c>
       <c r="G27" s="28" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -2444,7 +2474,7 @@
         <v>121</v>
       </c>
       <c r="G28" s="31" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -2467,7 +2497,7 @@
         <v>121</v>
       </c>
       <c r="G29" s="28" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -2490,7 +2520,7 @@
         <v>121</v>
       </c>
       <c r="G30" s="31" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -2513,7 +2543,7 @@
         <v>121</v>
       </c>
       <c r="G31" s="28" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -2536,7 +2566,7 @@
         <v>121</v>
       </c>
       <c r="G32" s="31" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -2559,7 +2589,7 @@
         <v>121</v>
       </c>
       <c r="G33" s="28" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -2582,7 +2612,7 @@
         <v>121</v>
       </c>
       <c r="G34" s="31" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/private/intl/do/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/do/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Prestaciones laborales»: pones tus fechas, tu salario promedio y cómo terminó el contrato, y te dice el preaviso, la cesantía, las vacaciones y la regalía.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 20/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 21/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -293,7 +293,7 @@
     <t>Tablas oficiales de República Dominicana</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 20/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 21/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -1620,7 +1620,7 @@
         <v>57</v>
       </c>
       <c r="B6" s="17">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>58</v>

--- a/private/intl/do/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/do/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Prestaciones laborales»: pones tus fechas, tu salario promedio y cómo terminó el contrato, y te dice el preaviso, la cesantía, las vacaciones y la regalía.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 21/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 22/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -293,7 +293,7 @@
     <t>Tablas oficiales de República Dominicana</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 21/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 22/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -1620,7 +1620,7 @@
         <v>57</v>
       </c>
       <c r="B6" s="17">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>58</v>
